--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260603.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260603.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>977,832,462</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>977,832,462</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>美律實業</t>
+          <t>富邦媒體</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,440,000</t>
+          <t>770,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦媒體</t>
+          <t>美律實業</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>2,440,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
